--- a/owlcms/src/main/resources/agegroups/USAW-AgeGroups_en_US.xlsx
+++ b/owlcms/src/main/resources/agegroups/USAW-AgeGroups_en_US.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\agegroups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7321FD86-3561-416E-B842-347868EFDD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165F37AF-AFA7-419F-BF0C-E33F188AD154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6060" yWindow="2565" windowWidth="21600" windowHeight="12105" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AgeGroups" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="66">
   <si>
     <t>code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>QMasters</t>
+  </si>
+  <si>
+    <t>QYouth</t>
+  </si>
+  <si>
+    <t>Qpoints</t>
   </si>
 </sst>
 </file>
@@ -647,6 +653,9 @@
         <v>0</v>
       </c>
       <c r="H2" s="7"/>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
       <c r="J2" s="1">
         <v>30</v>
       </c>
@@ -707,6 +716,9 @@
         <v>1</v>
       </c>
       <c r="H3" s="7"/>
+      <c r="I3" t="s">
+        <v>64</v>
+      </c>
       <c r="J3" s="1">
         <v>30</v>
       </c>
@@ -767,6 +779,9 @@
         <v>1</v>
       </c>
       <c r="H4" s="7"/>
+      <c r="I4" t="s">
+        <v>64</v>
+      </c>
       <c r="J4" s="1"/>
       <c r="L4" s="2">
         <v>36</v>
@@ -826,6 +841,9 @@
         <v>1</v>
       </c>
       <c r="H5" s="7"/>
+      <c r="I5" t="s">
+        <v>65</v>
+      </c>
       <c r="J5" s="1"/>
       <c r="M5" s="1">
         <v>40</v>
@@ -885,6 +903,9 @@
         <v>0</v>
       </c>
       <c r="H6" s="7"/>
+      <c r="I6" t="s">
+        <v>65</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1">
@@ -944,6 +965,9 @@
         <v>0</v>
       </c>
       <c r="H7" s="7"/>
+      <c r="I7" t="s">
+        <v>65</v>
+      </c>
       <c r="J7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1">
@@ -1871,6 +1895,9 @@
         <v>1</v>
       </c>
       <c r="H22" s="7"/>
+      <c r="I22" t="s">
+        <v>65</v>
+      </c>
       <c r="J22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1">
@@ -1930,6 +1957,9 @@
         <v>1</v>
       </c>
       <c r="H23" s="7"/>
+      <c r="I23" t="s">
+        <v>65</v>
+      </c>
       <c r="J23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1">
@@ -1989,6 +2019,9 @@
         <v>0</v>
       </c>
       <c r="H24" s="7"/>
+      <c r="I24" t="s">
+        <v>65</v>
+      </c>
       <c r="J24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1">
@@ -2050,7 +2083,9 @@
       <c r="H25" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I25" s="7"/>
+      <c r="I25" t="s">
+        <v>65</v>
+      </c>
       <c r="J25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
@@ -2137,6 +2172,9 @@
         <v>0</v>
       </c>
       <c r="H27" s="7"/>
+      <c r="I27" t="s">
+        <v>64</v>
+      </c>
       <c r="J27" s="1">
         <v>32</v>
       </c>
@@ -2197,6 +2235,9 @@
         <v>1</v>
       </c>
       <c r="H28" s="7"/>
+      <c r="I28" t="s">
+        <v>64</v>
+      </c>
       <c r="J28" s="1">
         <v>32</v>
       </c>
@@ -2257,6 +2298,9 @@
         <v>1</v>
       </c>
       <c r="H29" s="7"/>
+      <c r="I29" t="s">
+        <v>64</v>
+      </c>
       <c r="J29" s="1"/>
       <c r="L29" s="2">
         <v>39</v>
@@ -2315,6 +2359,9 @@
         <v>1</v>
       </c>
       <c r="H30" s="7"/>
+      <c r="I30" t="s">
+        <v>64</v>
+      </c>
       <c r="J30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1">
@@ -2373,6 +2420,9 @@
         <v>0</v>
       </c>
       <c r="H31" s="7"/>
+      <c r="I31" t="s">
+        <v>65</v>
+      </c>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -2433,6 +2483,9 @@
         <v>0</v>
       </c>
       <c r="H32" s="7"/>
+      <c r="I32" t="s">
+        <v>65</v>
+      </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -3375,6 +3428,9 @@
         <v>1</v>
       </c>
       <c r="H47" s="7"/>
+      <c r="I47" t="s">
+        <v>65</v>
+      </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -3435,6 +3491,9 @@
         <v>1</v>
       </c>
       <c r="H48" s="7"/>
+      <c r="I48" t="s">
+        <v>65</v>
+      </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -3495,6 +3554,9 @@
         <v>0</v>
       </c>
       <c r="H49" s="7"/>
+      <c r="I49" t="s">
+        <v>65</v>
+      </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -3557,7 +3619,9 @@
       <c r="H50" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I50" s="7"/>
+      <c r="I50" t="s">
+        <v>65</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
